--- a/But_D1.xlsx
+++ b/But_D1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="7"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="BUT D1 " sheetId="1" state="visible" r:id="rId3"/>
@@ -16,11 +16,13 @@
     <sheet name="MTP" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="SPORTING" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="AVION" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="KINGERSHEIM" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">ACASA!$A$1:$M$57</definedName>
     <definedName function="false" hidden="true" localSheetId="7" name="_xlnm._FilterDatabase" vbProcedure="false">AVION!$A$1:$L$68</definedName>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'BUT D1 '!$A$1:$M$693</definedName>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">KINGERSHEIM!$A$1:$M$21</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">LAVAL!$A$1:$M$106</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">MTP!$A$1:$M$78</definedName>
     <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">SPORTING!$A$1:$M$88</definedName>
@@ -35,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6695" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6828" uniqueCount="191">
   <si>
     <t xml:space="preserve">journee</t>
   </si>
@@ -607,23 +609,7 @@
     <t xml:space="preserve">pénalty</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">a</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="13"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">attaque placée</t>
-    </r>
+    <t xml:space="preserve">aattaque placée</t>
   </si>
 </sst>
 </file>
@@ -633,7 +619,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -683,11 +669,6 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="13"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -731,7 +712,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -768,12 +749,16 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -826,6 +811,10 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -1450,7 +1439,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
     </row>
-    <row r="13" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>1</v>
       </c>
@@ -1491,7 +1480,7 @@
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
     </row>
-    <row r="14" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>1</v>
       </c>
@@ -1696,7 +1685,7 @@
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
     </row>
-    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
         <v>1</v>
       </c>
@@ -1737,7 +1726,7 @@
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
     </row>
-    <row r="20" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
         <v>1</v>
       </c>
@@ -1778,7 +1767,7 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
     </row>
-    <row r="21" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
         <v>1</v>
       </c>
@@ -1819,7 +1808,7 @@
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
     </row>
-    <row r="22" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="n">
         <v>1</v>
       </c>
@@ -2975,7 +2964,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="51" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="n">
         <v>2</v>
       </c>
@@ -3013,7 +3002,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="52" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="n">
         <v>2</v>
       </c>
@@ -3051,7 +3040,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2" t="n">
         <v>2</v>
       </c>
@@ -3393,7 +3382,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="n">
         <v>2</v>
       </c>
@@ -3431,7 +3420,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="2" t="n">
         <v>2</v>
       </c>
@@ -3469,7 +3458,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="2" t="n">
         <v>2</v>
       </c>
@@ -3849,7 +3838,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="74" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="n">
         <v>2</v>
       </c>
@@ -4153,7 +4142,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="82" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="82" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="n">
         <v>3</v>
       </c>
@@ -4419,7 +4408,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="89" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="2" t="n">
         <v>3</v>
       </c>
@@ -4761,7 +4750,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="98" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="2" t="n">
         <v>3</v>
       </c>
@@ -4951,7 +4940,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="103" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="103" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2" t="n">
         <v>3</v>
       </c>
@@ -5217,7 +5206,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="110" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="n">
         <v>4</v>
       </c>
@@ -5407,7 +5396,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="115" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="n">
         <v>4</v>
       </c>
@@ -5445,7 +5434,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="116" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2" t="n">
         <v>4</v>
       </c>
@@ -5749,7 +5738,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="124" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2" t="n">
         <v>4</v>
       </c>
@@ -6509,7 +6498,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="144" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="n">
         <v>5</v>
       </c>
@@ -6737,7 +6726,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="150" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="n">
         <v>5</v>
       </c>
@@ -6775,7 +6764,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="151" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="n">
         <v>5</v>
       </c>
@@ -6813,7 +6802,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="152" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="n">
         <v>5</v>
       </c>
@@ -7003,7 +6992,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="157" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="n">
         <v>5</v>
       </c>
@@ -7117,7 +7106,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="160" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2" t="n">
         <v>5</v>
       </c>
@@ -7687,7 +7676,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="175" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="175" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2" t="n">
         <v>6</v>
       </c>
@@ -7725,7 +7714,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="176" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="176" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2" t="n">
         <v>6</v>
       </c>
@@ -7915,7 +7904,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="181" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="181" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="2" t="n">
         <v>6</v>
       </c>
@@ -8257,7 +8246,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="190" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="2" t="n">
         <v>6</v>
       </c>
@@ -8295,7 +8284,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="191" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="2" t="n">
         <v>6</v>
       </c>
@@ -9397,7 +9386,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="220" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2" t="n">
         <v>7</v>
       </c>
@@ -9701,7 +9690,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="228" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2" t="n">
         <v>7</v>
       </c>
@@ -9777,7 +9766,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="230" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="2" t="n">
         <v>7</v>
       </c>
@@ -10081,7 +10070,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="238" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2" t="n">
         <v>8</v>
       </c>
@@ -10119,7 +10108,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="239" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="239" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2" t="n">
         <v>8</v>
       </c>
@@ -10157,7 +10146,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="240" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="240" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2" t="n">
         <v>8</v>
       </c>
@@ -10613,7 +10602,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="252" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="252" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2" t="n">
         <v>8</v>
       </c>
@@ -10689,7 +10678,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="254" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="254" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2" t="n">
         <v>8</v>
       </c>
@@ -10765,7 +10754,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="256" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="256" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2" t="n">
         <v>8</v>
       </c>
@@ -10803,7 +10792,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="257" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="257" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2" t="n">
         <v>8</v>
       </c>
@@ -12361,7 +12350,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="298" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="298" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A298" s="2" t="n">
         <v>10</v>
       </c>
@@ -14033,7 +14022,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="342" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="342" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2" t="n">
         <v>11</v>
       </c>
@@ -15021,7 +15010,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="368" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="368" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A368" s="2" t="n">
         <v>12</v>
       </c>
@@ -15971,7 +15960,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="393" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="393" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A393" s="2" t="n">
         <v>12</v>
       </c>
@@ -16047,7 +16036,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="395" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="395" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2" t="n">
         <v>12</v>
       </c>
@@ -16465,7 +16454,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="406" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="406" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A406" s="2" t="n">
         <v>13</v>
       </c>
@@ -16504,7 +16493,7 @@
       </c>
       <c r="M406" s="1"/>
     </row>
-    <row r="407" s="2" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="407" s="2" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A407" s="2" t="n">
         <v>13</v>
       </c>
@@ -17205,7 +17194,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="425" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="425" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A425" s="2" t="n">
         <v>13</v>
       </c>
@@ -17243,7 +17232,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="426" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="426" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A426" s="2" t="n">
         <v>13</v>
       </c>
@@ -17663,7 +17652,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="437" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="437" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A437" s="2" t="n">
         <v>13</v>
       </c>
@@ -18424,7 +18413,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="457" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="457" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A457" s="2" t="n">
         <v>14</v>
       </c>
@@ -18918,7 +18907,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="470" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="470" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A470" s="2" t="n">
         <v>14</v>
       </c>
@@ -19032,7 +19021,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="473" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="473" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A473" s="2" t="n">
         <v>14</v>
       </c>
@@ -19955,7 +19944,7 @@
       </c>
       <c r="M496" s="2"/>
     </row>
-    <row r="497" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="497" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A497" s="2" t="n">
         <v>15</v>
       </c>
@@ -20381,7 +20370,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="508" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="508" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A508" s="2" t="n">
         <v>15</v>
       </c>
@@ -20419,7 +20408,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="509" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="509" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A509" s="2" t="n">
         <v>15</v>
       </c>
@@ -20457,7 +20446,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="510" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="510" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A510" s="2" t="n">
         <v>15</v>
       </c>
@@ -21103,7 +21092,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="527" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="527" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A527" s="2" t="n">
         <v>15</v>
       </c>
@@ -21333,7 +21322,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="533" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="533" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A533" s="2" t="n">
         <v>16</v>
       </c>
@@ -21827,7 +21816,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="546" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="546" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A546" s="2" t="n">
         <v>16</v>
       </c>
@@ -21865,7 +21854,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="547" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="547" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A547" s="2" t="n">
         <v>16</v>
       </c>
@@ -22283,7 +22272,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="558" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="558" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A558" s="2" t="n">
         <v>16</v>
       </c>
@@ -22321,7 +22310,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="559" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="559" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A559" s="2" t="n">
         <v>16</v>
       </c>
@@ -22929,7 +22918,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="575" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="575" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A575" s="2" t="n">
         <v>17</v>
       </c>
@@ -25649,7 +25638,7 @@
       <c r="Q643" s="1"/>
       <c r="R643" s="1"/>
     </row>
-    <row r="644" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="644" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A644" s="1" t="n">
         <v>19</v>
       </c>
@@ -25693,7 +25682,7 @@
       <c r="Q644" s="1"/>
       <c r="R644" s="1"/>
     </row>
-    <row r="645" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="645" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A645" s="1" t="n">
         <v>19</v>
       </c>
@@ -25737,7 +25726,7 @@
       <c r="Q645" s="1"/>
       <c r="R645" s="1"/>
     </row>
-    <row r="646" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="646" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A646" s="1" t="n">
         <v>19</v>
       </c>
@@ -25781,7 +25770,7 @@
       <c r="Q646" s="1"/>
       <c r="R646" s="1"/>
     </row>
-    <row r="647" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="647" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A647" s="1" t="n">
         <v>19</v>
       </c>
@@ -25825,7 +25814,7 @@
       <c r="Q647" s="1"/>
       <c r="R647" s="1"/>
     </row>
-    <row r="648" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="648" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A648" s="1" t="n">
         <v>19</v>
       </c>
@@ -25869,7 +25858,7 @@
       <c r="Q648" s="1"/>
       <c r="R648" s="1"/>
     </row>
-    <row r="649" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="649" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A649" s="1" t="n">
         <v>19</v>
       </c>
@@ -25913,7 +25902,7 @@
       <c r="Q649" s="1"/>
       <c r="R649" s="1"/>
     </row>
-    <row r="650" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="650" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A650" s="1" t="n">
         <v>19</v>
       </c>
@@ -25957,7 +25946,7 @@
       <c r="Q650" s="1"/>
       <c r="R650" s="1"/>
     </row>
-    <row r="651" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="651" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A651" s="1" t="n">
         <v>19</v>
       </c>
@@ -26001,7 +25990,7 @@
       <c r="Q651" s="1"/>
       <c r="R651" s="1"/>
     </row>
-    <row r="652" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="652" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A652" s="1" t="n">
         <v>19</v>
       </c>
@@ -26045,7 +26034,7 @@
       <c r="Q652" s="1"/>
       <c r="R652" s="1"/>
     </row>
-    <row r="653" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="653" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A653" s="1" t="n">
         <v>19</v>
       </c>
@@ -26089,7 +26078,7 @@
       <c r="Q653" s="1"/>
       <c r="R653" s="1"/>
     </row>
-    <row r="654" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="654" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A654" s="1" t="n">
         <v>19</v>
       </c>
@@ -26133,7 +26122,7 @@
       <c r="Q654" s="1"/>
       <c r="R654" s="1"/>
     </row>
-    <row r="655" s="4" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="655" s="4" customFormat="true" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A655" s="1" t="n">
         <v>19</v>
       </c>
@@ -26177,7 +26166,7 @@
       <c r="Q655" s="1"/>
       <c r="R655" s="1"/>
     </row>
-    <row r="656" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="656" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A656" s="1" t="n">
         <v>19</v>
       </c>
@@ -26221,7 +26210,7 @@
       <c r="Q656" s="4"/>
       <c r="R656" s="4"/>
     </row>
-    <row r="657" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="657" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A657" s="1" t="n">
         <v>19</v>
       </c>
@@ -26259,7 +26248,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="658" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="658" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A658" s="1" t="n">
         <v>19</v>
       </c>
@@ -26297,7 +26286,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="659" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="659" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A659" s="1" t="n">
         <v>19</v>
       </c>
@@ -26335,7 +26324,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="660" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="660" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A660" s="4" t="n">
         <v>20</v>
       </c>
@@ -26373,7 +26362,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="661" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="661" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A661" s="1" t="n">
         <v>20</v>
       </c>
@@ -26487,7 +26476,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="664" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="664" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A664" s="1" t="n">
         <v>20</v>
       </c>
@@ -27133,7 +27122,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="681" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="681" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A681" s="1" t="n">
         <v>20</v>
       </c>
@@ -27551,7 +27540,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="692" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="692" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A692" s="1" t="n">
         <v>20</v>
       </c>
@@ -27589,7 +27578,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="693" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="693" customFormat="false" ht="16.15" hidden="true" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A693" s="1" t="n">
         <v>20</v>
       </c>
@@ -27631,7 +27620,7 @@
   <autoFilter ref="A1:M693">
     <filterColumn colId="3">
       <filters>
-        <filter val="AS AVION FUTSAL"/>
+        <filter val="FC KINGERSHEIM"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -39959,7 +39948,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="13" min="13" style="2" width="23.26"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="39.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="42.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -43188,7 +43177,7 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="18" min="12" style="1" width="25.21"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="39.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="56.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -50700,4 +50689,891 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultColWidth="24.53515625" defaultRowHeight="19.55" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="1" style="11" width="24.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="6" style="11" width="7.04"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="12" style="11" width="24.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="M3" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M5" s="11" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="M8" s="11" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M9" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M10" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="M13" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M14" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="M15" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="M16" s="11" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="M17" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="H18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J18" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="M18" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G19" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="H19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="I19" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="K19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L19" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="M19" s="11" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="G20" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="H20" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="I20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="M20" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="19.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="H21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="M21" s="11" t="s">
+        <v>181</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:M21"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Normal"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Normal"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/But_D1.xlsx
+++ b/But_D1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="BUT D1 " sheetId="1" state="visible" r:id="rId3"/>
@@ -29110,7 +29110,7 @@
         <v>1</v>
       </c>
       <c r="L740" s="1" t="s">
-        <v>15</v>
+        <v>89</v>
       </c>
     </row>
     <row r="741" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
